--- a/OPEC_Human_Verification.xlsx
+++ b/OPEC_Human_Verification.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/datle/Desktop/1 Research/From_Words_to_Barrels_Measuring_the_Incremental_Information_Content_of_OPEC_Narratives_for_Oil_Price/outputs/019fc64f-human-validation-combined/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3AD3409-23F4-904C-B91C-94C54660B216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5949797-6BE3-0B48-A823-8AF9DD826A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Huong dan" sheetId="1" r:id="rId1"/>
@@ -5976,9 +5976,6 @@
     <t>participating in the Declaration of Cooperation, with the exception of Mexico, and as a result, the agreement is conditional on the consent of Mexico.</t>
   </si>
   <si>
-    <t>anhdat le</t>
-  </si>
-  <si>
     <t>File không chứa nhãn mô hình hay bảng ánh xạ riêng. Ngày tháng/tên sự kiện vẫn có thể xuất hiện trong văn bản nguồn: không coi đây là làm mù hoàn toàn danh tính sự kiện.</t>
   </si>
   <si>
@@ -6289,6 +6286,9 @@
   </si>
   <si>
     <t>Tái khẳng định quyết định/lịch tăng đã có trước; không phải thay đổi ròng mới tại sự kiện này.</t>
+  </si>
+  <si>
+    <t>v1</t>
   </si>
 </sst>
 </file>
@@ -6673,7 +6673,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1308</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="76" customHeight="1">
@@ -6713,7 +6713,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="76" customHeight="1">
@@ -6896,23 +6896,23 @@
         <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="3">
         <v>4</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>1328</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>1329</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" customHeight="1">
@@ -6923,17 +6923,17 @@
         <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60" customHeight="1">
@@ -6944,23 +6944,23 @@
         <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <v>3</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1">
@@ -6971,17 +6971,17 @@
         <v>57</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="60" customHeight="1">
@@ -6992,23 +6992,23 @@
         <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3">
         <v>4</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="60" customHeight="1">
@@ -7019,17 +7019,17 @@
         <v>61</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1">
@@ -7040,10 +7040,10 @@
         <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E8" s="4">
         <v>0</v>
@@ -7052,13 +7052,13 @@
         <v>4</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="60" customHeight="1">
@@ -7069,23 +7069,23 @@
         <v>65</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3">
         <v>4</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="60" customHeight="1">
@@ -7096,23 +7096,23 @@
         <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="3">
         <v>4</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="60" customHeight="1">
@@ -7123,23 +7123,23 @@
         <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="3">
         <v>4</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="60" customHeight="1">
@@ -7150,17 +7150,17 @@
         <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="4"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="60" customHeight="1">
@@ -7171,17 +7171,17 @@
         <v>73</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="60" customHeight="1">
@@ -7192,23 +7192,23 @@
         <v>75</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="3">
         <v>4</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="60" customHeight="1">
@@ -7219,23 +7219,23 @@
         <v>77</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="3">
         <v>3</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="60" customHeight="1">
@@ -7246,17 +7246,17 @@
         <v>79</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" customHeight="1">
@@ -7267,17 +7267,17 @@
         <v>81</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="4"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" customHeight="1">
@@ -7288,17 +7288,17 @@
         <v>83</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="4"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" customHeight="1">
@@ -7309,23 +7309,23 @@
         <v>85</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="3">
         <v>4</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" customHeight="1">
@@ -7336,23 +7336,23 @@
         <v>87</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="3">
         <v>4</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" customHeight="1">
@@ -7363,17 +7363,17 @@
         <v>89</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" customHeight="1">
@@ -7384,23 +7384,23 @@
         <v>91</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="3">
         <v>4</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" customHeight="1">
@@ -7411,17 +7411,17 @@
         <v>93</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" customHeight="1">
@@ -7432,17 +7432,17 @@
         <v>95</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" customHeight="1">
@@ -7453,17 +7453,17 @@
         <v>97</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" customHeight="1">
@@ -7474,10 +7474,10 @@
         <v>99</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E26" s="4">
         <v>0.54800000000000004</v>
@@ -7486,13 +7486,13 @@
         <v>5</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>1371</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>1372</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" customHeight="1">
@@ -7503,23 +7503,23 @@
         <v>101</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="3">
         <v>4</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" customHeight="1">
@@ -7530,17 +7530,17 @@
         <v>103</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="4"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" customHeight="1">
@@ -7551,23 +7551,23 @@
         <v>105</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="3">
         <v>4</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" customHeight="1">
@@ -7578,10 +7578,10 @@
         <v>107</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E30" s="4">
         <v>0.5</v>
@@ -7590,13 +7590,13 @@
         <v>5</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>1375</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>1376</v>
-      </c>
       <c r="I30" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" customHeight="1">
@@ -7607,10 +7607,10 @@
         <v>109</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E31" s="4">
         <v>0.41099999999999998</v>
@@ -7619,13 +7619,13 @@
         <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" customHeight="1">
@@ -7636,23 +7636,23 @@
         <v>111</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="3">
         <v>4</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="60" customHeight="1">
@@ -7663,23 +7663,23 @@
         <v>113</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="3">
         <v>4</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="60" customHeight="1">
@@ -7690,17 +7690,17 @@
         <v>115</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="60" customHeight="1">
@@ -7711,17 +7711,17 @@
         <v>117</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="4"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="60" customHeight="1">
@@ -7732,10 +7732,10 @@
         <v>119</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E36" s="4">
         <v>0.41099999999999998</v>
@@ -7744,13 +7744,13 @@
         <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="60" customHeight="1">
@@ -7761,23 +7761,23 @@
         <v>121</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="3">
         <v>4</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="60" customHeight="1">
@@ -7788,17 +7788,17 @@
         <v>123</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="60" customHeight="1">
@@ -7809,23 +7809,23 @@
         <v>125</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="3">
         <v>3</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="60" customHeight="1">
@@ -7836,23 +7836,23 @@
         <v>127</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="3">
         <v>4</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="60" customHeight="1">
@@ -7863,23 +7863,23 @@
         <v>129</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="3">
         <v>4</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="60" customHeight="1">
@@ -7890,23 +7890,23 @@
         <v>131</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="3">
         <v>4</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="60" customHeight="1">
@@ -7917,23 +7917,23 @@
         <v>133</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="3">
         <v>3</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="60" customHeight="1">
@@ -7944,17 +7944,17 @@
         <v>135</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="60" customHeight="1">
@@ -7965,23 +7965,23 @@
         <v>137</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="3">
         <v>4</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="60" customHeight="1">
@@ -7992,17 +7992,17 @@
         <v>139</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="4"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="60" customHeight="1">
@@ -8013,23 +8013,23 @@
         <v>141</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="3">
         <v>4</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="60" customHeight="1">
@@ -8040,23 +8040,23 @@
         <v>143</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="3">
         <v>4</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="60" customHeight="1">
@@ -8067,23 +8067,23 @@
         <v>145</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="3">
         <v>4</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="60" customHeight="1">
@@ -8094,23 +8094,23 @@
         <v>147</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="3">
         <v>4</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="60" customHeight="1">
@@ -8121,17 +8121,17 @@
         <v>149</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="4"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="60" customHeight="1">
@@ -8142,17 +8142,17 @@
         <v>151</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="4"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="60" customHeight="1">
@@ -8163,17 +8163,17 @@
         <v>153</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="4"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="60" customHeight="1">
@@ -8184,17 +8184,17 @@
         <v>155</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="4"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="60" customHeight="1">
@@ -8205,17 +8205,17 @@
         <v>157</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="4"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="60" customHeight="1">
@@ -8226,23 +8226,23 @@
         <v>159</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="3">
         <v>4</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="60" customHeight="1">
@@ -8253,23 +8253,23 @@
         <v>161</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="3">
         <v>4</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="60" customHeight="1">
@@ -8280,23 +8280,23 @@
         <v>163</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="3">
         <v>4</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="60" customHeight="1">
@@ -8307,23 +8307,23 @@
         <v>165</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="3">
         <v>4</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="60" customHeight="1">
@@ -8334,23 +8334,23 @@
         <v>167</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="3">
         <v>4</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="60" customHeight="1">
@@ -8361,23 +8361,23 @@
         <v>169</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="3">
         <v>3</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="60" customHeight="1">
@@ -8388,23 +8388,23 @@
         <v>171</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="3">
         <v>4</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="60" customHeight="1">
@@ -8415,17 +8415,17 @@
         <v>173</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="4"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="60" customHeight="1">
@@ -8436,23 +8436,23 @@
         <v>175</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="3">
         <v>4</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="60" customHeight="1">
@@ -8463,23 +8463,23 @@
         <v>177</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="3">
         <v>4</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="60" customHeight="1">
@@ -8490,10 +8490,10 @@
         <v>179</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E66" s="4">
         <v>0</v>
@@ -8502,13 +8502,13 @@
         <v>4</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="60" customHeight="1">
@@ -8519,23 +8519,23 @@
         <v>181</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="3">
         <v>4</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="60" customHeight="1">
@@ -8546,17 +8546,17 @@
         <v>183</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="4"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="60" customHeight="1">
@@ -8567,23 +8567,23 @@
         <v>185</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="3">
         <v>4</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="60" customHeight="1">
@@ -8594,17 +8594,17 @@
         <v>187</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="4"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="60" customHeight="1">
@@ -8615,17 +8615,17 @@
         <v>189</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="4"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="60" customHeight="1">
@@ -8636,17 +8636,17 @@
         <v>191</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="4"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="60" customHeight="1">
@@ -8657,10 +8657,10 @@
         <v>193</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E73" s="4">
         <v>0.54700000000000004</v>
@@ -8669,13 +8669,13 @@
         <v>5</v>
       </c>
       <c r="G73" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>1396</v>
       </c>
-      <c r="H73" s="3" t="s">
-        <v>1397</v>
-      </c>
       <c r="I73" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="60" customHeight="1">
@@ -8686,17 +8686,17 @@
         <v>195</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="4"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="60" customHeight="1">
@@ -8707,10 +8707,10 @@
         <v>197</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
@@ -8719,13 +8719,13 @@
         <v>4</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="60" customHeight="1">
@@ -8736,23 +8736,23 @@
         <v>199</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="3">
         <v>3</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="60" customHeight="1">
@@ -8763,17 +8763,17 @@
         <v>201</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="4"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="60" customHeight="1">
@@ -8784,23 +8784,23 @@
         <v>203</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="3">
         <v>4</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="60" customHeight="1">
@@ -8811,23 +8811,23 @@
         <v>205</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="3">
         <v>3</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="60" customHeight="1">
@@ -8838,23 +8838,23 @@
         <v>207</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="3">
         <v>4</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="60" customHeight="1">
@@ -8865,17 +8865,17 @@
         <v>209</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="4"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="60" customHeight="1">
@@ -8886,23 +8886,23 @@
         <v>211</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="3">
         <v>4</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="60" customHeight="1">
@@ -8913,10 +8913,10 @@
         <v>213</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E83" s="4">
         <v>0.41099999999999998</v>
@@ -8925,13 +8925,13 @@
         <v>5</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="60" customHeight="1">
@@ -8942,10 +8942,10 @@
         <v>215</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
@@ -8954,13 +8954,13 @@
         <v>4</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="60" customHeight="1">
@@ -8971,23 +8971,23 @@
         <v>217</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="3">
         <v>4</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="60" customHeight="1">
@@ -8998,23 +8998,23 @@
         <v>219</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E86" s="4"/>
       <c r="F86" s="3">
         <v>4</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="60" customHeight="1">
@@ -9025,23 +9025,23 @@
         <v>221</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="3">
         <v>3</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="60" customHeight="1">
@@ -9052,17 +9052,17 @@
         <v>223</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="4"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="60" customHeight="1">
@@ -9073,17 +9073,17 @@
         <v>225</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="4"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="60" customHeight="1">
@@ -9094,23 +9094,23 @@
         <v>227</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="3">
         <v>3</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="60" customHeight="1">
@@ -9121,23 +9121,23 @@
         <v>229</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="3">
         <v>4</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="60" customHeight="1">
@@ -9148,23 +9148,23 @@
         <v>231</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="3">
         <v>4</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="60" customHeight="1">
@@ -9175,17 +9175,17 @@
         <v>233</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="4"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="60" customHeight="1">
@@ -9196,23 +9196,23 @@
         <v>235</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="3">
         <v>3</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="60" customHeight="1">
@@ -9223,17 +9223,17 @@
         <v>237</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="4"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="60" customHeight="1">
@@ -9244,17 +9244,17 @@
         <v>239</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="4"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="60" customHeight="1">
@@ -9265,23 +9265,23 @@
         <v>241</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="3">
         <v>4</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="60" customHeight="1">
@@ -9292,23 +9292,23 @@
         <v>243</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="3">
         <v>4</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="60" customHeight="1">
@@ -9319,17 +9319,17 @@
         <v>245</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="4"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="60" customHeight="1">
@@ -9340,17 +9340,17 @@
         <v>247</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="4"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="60" customHeight="1">
@@ -9361,17 +9361,17 @@
         <v>249</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="4"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="60" customHeight="1">
@@ -9382,23 +9382,23 @@
         <v>251</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="3">
         <v>3</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="60" customHeight="1">
@@ -9409,23 +9409,23 @@
         <v>253</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="3">
         <v>4</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="60" customHeight="1">
@@ -9436,17 +9436,17 @@
         <v>255</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="4"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="60" customHeight="1">
@@ -9457,23 +9457,23 @@
         <v>257</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="3">
         <v>4</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="60" customHeight="1">
@@ -9484,23 +9484,23 @@
         <v>259</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="3">
         <v>3</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="60" customHeight="1">
@@ -9511,17 +9511,17 @@
         <v>261</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="4"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="60" customHeight="1">
@@ -9532,17 +9532,17 @@
         <v>263</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="4"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
   </sheetData>
@@ -9624,7 +9624,7 @@
         <v>270</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E2" s="3">
         <v>-0.6</v>
@@ -9633,13 +9633,13 @@
         <v>271</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" customHeight="1">
@@ -9653,22 +9653,22 @@
         <v>270</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60" customHeight="1">
@@ -9682,7 +9682,7 @@
         <v>270</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5" t="s">
@@ -9690,10 +9690,10 @@
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1">
@@ -9707,7 +9707,7 @@
         <v>270</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="5" t="s">
@@ -9715,10 +9715,10 @@
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="60" customHeight="1">
@@ -9732,7 +9732,7 @@
         <v>276</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E6" s="3">
         <v>0.8</v>
@@ -9741,13 +9741,13 @@
         <v>271</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="60" customHeight="1">
@@ -9761,22 +9761,22 @@
         <v>276</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>1318</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>1348</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>1319</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1">
@@ -9790,7 +9790,7 @@
         <v>276</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E8" s="3">
         <v>0.6</v>
@@ -9799,13 +9799,13 @@
         <v>271</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="60" customHeight="1">
@@ -9819,7 +9819,7 @@
         <v>276</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="5" t="s">
@@ -9827,10 +9827,10 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="60" customHeight="1">
@@ -9844,7 +9844,7 @@
         <v>278</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="5" t="s">
@@ -9852,10 +9852,10 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="60" customHeight="1">
@@ -9869,7 +9869,7 @@
         <v>278</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>271</v>
@@ -9877,10 +9877,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="60" customHeight="1">
@@ -9894,7 +9894,7 @@
         <v>278</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="5" t="s">
@@ -9902,10 +9902,10 @@
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="60" customHeight="1">
@@ -9919,7 +9919,7 @@
         <v>278</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="5" t="s">
@@ -9927,10 +9927,10 @@
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="60" customHeight="1">
@@ -9944,7 +9944,7 @@
         <v>280</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E14" s="3">
         <v>-0.7</v>
@@ -9953,13 +9953,13 @@
         <v>271</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="60" customHeight="1">
@@ -9973,22 +9973,22 @@
         <v>280</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="60" customHeight="1">
@@ -10002,7 +10002,7 @@
         <v>280</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E16" s="3">
         <v>0.6</v>
@@ -10011,13 +10011,13 @@
         <v>271</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" customHeight="1">
@@ -10031,7 +10031,7 @@
         <v>280</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="5" t="s">
@@ -10039,10 +10039,10 @@
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" customHeight="1">
@@ -10056,7 +10056,7 @@
         <v>282</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -10065,13 +10065,13 @@
         <v>271</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" customHeight="1">
@@ -10085,22 +10085,22 @@
         <v>282</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" customHeight="1">
@@ -10114,7 +10114,7 @@
         <v>282</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="5" t="s">
@@ -10122,10 +10122,10 @@
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" customHeight="1">
@@ -10139,7 +10139,7 @@
         <v>282</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="5" t="s">
@@ -10147,10 +10147,10 @@
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" customHeight="1">
@@ -10164,7 +10164,7 @@
         <v>284</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -10173,13 +10173,13 @@
         <v>271</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" customHeight="1">
@@ -10193,22 +10193,22 @@
         <v>284</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" customHeight="1">
@@ -10222,7 +10222,7 @@
         <v>284</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="5" t="s">
@@ -10230,10 +10230,10 @@
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" customHeight="1">
@@ -10247,7 +10247,7 @@
         <v>284</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="5" t="s">
@@ -10255,10 +10255,10 @@
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" customHeight="1">
@@ -10272,7 +10272,7 @@
         <v>286</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="5" t="s">
@@ -10280,10 +10280,10 @@
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" customHeight="1">
@@ -10297,7 +10297,7 @@
         <v>286</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>271</v>
@@ -10305,10 +10305,10 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" customHeight="1">
@@ -10322,7 +10322,7 @@
         <v>286</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E28" s="3">
         <v>0.6</v>
@@ -10331,13 +10331,13 @@
         <v>271</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" customHeight="1">
@@ -10351,7 +10351,7 @@
         <v>286</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E29" s="3">
         <v>0.6</v>
@@ -10360,13 +10360,13 @@
         <v>271</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" customHeight="1">
@@ -10380,7 +10380,7 @@
         <v>288</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="5" t="s">
@@ -10388,10 +10388,10 @@
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" customHeight="1">
@@ -10405,7 +10405,7 @@
         <v>288</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>271</v>
@@ -10413,10 +10413,10 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" customHeight="1">
@@ -10430,7 +10430,7 @@
         <v>288</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="5" t="s">
@@ -10438,10 +10438,10 @@
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="60" customHeight="1">
@@ -10455,7 +10455,7 @@
         <v>288</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="5" t="s">
@@ -10463,10 +10463,10 @@
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="60" customHeight="1">
@@ -10480,7 +10480,7 @@
         <v>290</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="5" t="s">
@@ -10488,10 +10488,10 @@
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="60" customHeight="1">
@@ -10505,7 +10505,7 @@
         <v>290</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>271</v>
@@ -10513,10 +10513,10 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="60" customHeight="1">
@@ -10530,7 +10530,7 @@
         <v>290</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="5" t="s">
@@ -10538,10 +10538,10 @@
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="60" customHeight="1">
@@ -10555,7 +10555,7 @@
         <v>290</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="5" t="s">
@@ -10563,10 +10563,10 @@
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="60" customHeight="1">
@@ -10580,7 +10580,7 @@
         <v>292</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="5" t="s">
@@ -10588,10 +10588,10 @@
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="60" customHeight="1">
@@ -10605,7 +10605,7 @@
         <v>292</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>271</v>
@@ -10613,10 +10613,10 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="60" customHeight="1">
@@ -10630,7 +10630,7 @@
         <v>292</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="5" t="s">
@@ -10638,10 +10638,10 @@
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="60" customHeight="1">
@@ -10655,7 +10655,7 @@
         <v>292</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="5" t="s">
@@ -10663,10 +10663,10 @@
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="60" customHeight="1">
@@ -10680,7 +10680,7 @@
         <v>294</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="5" t="s">
@@ -10688,10 +10688,10 @@
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="60" customHeight="1">
@@ -10705,7 +10705,7 @@
         <v>294</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>271</v>
@@ -10713,10 +10713,10 @@
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="60" customHeight="1">
@@ -10730,7 +10730,7 @@
         <v>294</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="5" t="s">
@@ -10738,10 +10738,10 @@
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="60" customHeight="1">
@@ -10755,7 +10755,7 @@
         <v>294</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="5" t="s">
@@ -10763,10 +10763,10 @@
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="60" customHeight="1">
@@ -10780,7 +10780,7 @@
         <v>296</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="5" t="s">
@@ -10788,10 +10788,10 @@
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="60" customHeight="1">
@@ -10805,7 +10805,7 @@
         <v>296</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>271</v>
@@ -10813,10 +10813,10 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="60" customHeight="1">
@@ -10830,7 +10830,7 @@
         <v>296</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="5" t="s">
@@ -10838,10 +10838,10 @@
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="60" customHeight="1">
@@ -10855,7 +10855,7 @@
         <v>296</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="5" t="s">
@@ -10863,10 +10863,10 @@
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="60" customHeight="1">
@@ -10880,7 +10880,7 @@
         <v>298</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="5" t="s">
@@ -10888,10 +10888,10 @@
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="60" customHeight="1">
@@ -10905,7 +10905,7 @@
         <v>298</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>271</v>
@@ -10913,10 +10913,10 @@
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="60" customHeight="1">
@@ -10930,7 +10930,7 @@
         <v>298</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="5" t="s">
@@ -10938,10 +10938,10 @@
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="60" customHeight="1">
@@ -10955,7 +10955,7 @@
         <v>298</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="5" t="s">
@@ -10963,10 +10963,10 @@
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="60" customHeight="1">
@@ -10980,7 +10980,7 @@
         <v>300</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="5" t="s">
@@ -10988,10 +10988,10 @@
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="60" customHeight="1">
@@ -11005,7 +11005,7 @@
         <v>300</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>271</v>
@@ -11013,10 +11013,10 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="60" customHeight="1">
@@ -11030,7 +11030,7 @@
         <v>300</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="5" t="s">
@@ -11038,10 +11038,10 @@
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="60" customHeight="1">
@@ -11055,7 +11055,7 @@
         <v>300</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="5" t="s">
@@ -11063,10 +11063,10 @@
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="60" customHeight="1">
@@ -11080,7 +11080,7 @@
         <v>302</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="5" t="s">
@@ -11088,10 +11088,10 @@
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="60" customHeight="1">
@@ -11105,7 +11105,7 @@
         <v>302</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>271</v>
@@ -11113,10 +11113,10 @@
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="60" customHeight="1">
@@ -11130,7 +11130,7 @@
         <v>302</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="5" t="s">
@@ -11138,10 +11138,10 @@
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="60" customHeight="1">
@@ -11155,7 +11155,7 @@
         <v>302</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="5" t="s">
@@ -11163,10 +11163,10 @@
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="60" customHeight="1">
@@ -11180,7 +11180,7 @@
         <v>304</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="5" t="s">
@@ -11188,10 +11188,10 @@
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="60" customHeight="1">
@@ -11205,7 +11205,7 @@
         <v>304</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>271</v>
@@ -11213,10 +11213,10 @@
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="60" customHeight="1">
@@ -11230,7 +11230,7 @@
         <v>304</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="5" t="s">
@@ -11238,10 +11238,10 @@
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="60" customHeight="1">
@@ -11255,7 +11255,7 @@
         <v>304</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="5" t="s">
@@ -11263,10 +11263,10 @@
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="60" customHeight="1">
@@ -11280,7 +11280,7 @@
         <v>306</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="5" t="s">
@@ -11288,10 +11288,10 @@
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="60" customHeight="1">
@@ -11305,7 +11305,7 @@
         <v>306</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>271</v>
@@ -11313,10 +11313,10 @@
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="60" customHeight="1">
@@ -11330,7 +11330,7 @@
         <v>306</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="5" t="s">
@@ -11338,10 +11338,10 @@
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="60" customHeight="1">
@@ -11355,7 +11355,7 @@
         <v>306</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="5" t="s">
@@ -11363,10 +11363,10 @@
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="60" customHeight="1">
@@ -11380,7 +11380,7 @@
         <v>308</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="5" t="s">
@@ -11388,10 +11388,10 @@
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="60" customHeight="1">
@@ -11405,7 +11405,7 @@
         <v>308</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>271</v>
@@ -11413,10 +11413,10 @@
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="60" customHeight="1">
@@ -11430,7 +11430,7 @@
         <v>308</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E72" s="3">
         <v>0.6</v>
@@ -11439,13 +11439,13 @@
         <v>271</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="60" customHeight="1">
@@ -11459,7 +11459,7 @@
         <v>308</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="5" t="s">
@@ -11467,10 +11467,10 @@
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="60" customHeight="1">
@@ -11484,7 +11484,7 @@
         <v>310</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="5" t="s">
@@ -11492,10 +11492,10 @@
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="60" customHeight="1">
@@ -11509,7 +11509,7 @@
         <v>310</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>271</v>
@@ -11517,10 +11517,10 @@
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="60" customHeight="1">
@@ -11534,7 +11534,7 @@
         <v>310</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="5" t="s">
@@ -11542,10 +11542,10 @@
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="60" customHeight="1">
@@ -11559,7 +11559,7 @@
         <v>310</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="5" t="s">
@@ -11567,10 +11567,10 @@
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="60" customHeight="1">
@@ -11584,7 +11584,7 @@
         <v>312</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="5" t="s">
@@ -11592,10 +11592,10 @@
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="60" customHeight="1">
@@ -11609,7 +11609,7 @@
         <v>312</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>271</v>
@@ -11617,10 +11617,10 @@
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="60" customHeight="1">
@@ -11634,7 +11634,7 @@
         <v>312</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="5" t="s">
@@ -11642,10 +11642,10 @@
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="60" customHeight="1">
@@ -11659,7 +11659,7 @@
         <v>312</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="5" t="s">
@@ -11667,10 +11667,10 @@
       </c>
       <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="60" customHeight="1">
@@ -11684,7 +11684,7 @@
         <v>314</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="5" t="s">
@@ -11692,10 +11692,10 @@
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="60" customHeight="1">
@@ -11709,7 +11709,7 @@
         <v>314</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>271</v>
@@ -11717,10 +11717,10 @@
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="60" customHeight="1">
@@ -11734,7 +11734,7 @@
         <v>314</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E84" s="3">
         <v>0.6</v>
@@ -11743,13 +11743,13 @@
         <v>271</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="60" customHeight="1">
@@ -11763,7 +11763,7 @@
         <v>314</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E85" s="3">
         <v>0.6</v>
@@ -11772,13 +11772,13 @@
         <v>271</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="60" customHeight="1">
@@ -11792,7 +11792,7 @@
         <v>316</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="5" t="s">
@@ -11800,10 +11800,10 @@
       </c>
       <c r="G86" s="3"/>
       <c r="H86" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="60" customHeight="1">
@@ -11817,7 +11817,7 @@
         <v>316</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>271</v>
@@ -11825,10 +11825,10 @@
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="60" customHeight="1">
@@ -11842,7 +11842,7 @@
         <v>316</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="5" t="s">
@@ -11850,10 +11850,10 @@
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="60" customHeight="1">
@@ -11867,7 +11867,7 @@
         <v>316</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="5" t="s">
@@ -11875,10 +11875,10 @@
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="60" customHeight="1">
@@ -11892,7 +11892,7 @@
         <v>318</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="5" t="s">
@@ -11900,10 +11900,10 @@
       </c>
       <c r="G90" s="3"/>
       <c r="H90" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="60" customHeight="1">
@@ -11917,7 +11917,7 @@
         <v>318</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>271</v>
@@ -11925,10 +11925,10 @@
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="60" customHeight="1">
@@ -11942,7 +11942,7 @@
         <v>318</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E92" s="3">
         <v>0.6</v>
@@ -11951,13 +11951,13 @@
         <v>271</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="60" customHeight="1">
@@ -11971,7 +11971,7 @@
         <v>318</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="5" t="s">
@@ -11979,10 +11979,10 @@
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="60" customHeight="1">
@@ -11996,7 +11996,7 @@
         <v>320</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E94" s="3">
         <v>-0.7</v>
@@ -12005,13 +12005,13 @@
         <v>271</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="60" customHeight="1">
@@ -12025,22 +12025,22 @@
         <v>320</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="60" customHeight="1">
@@ -12054,7 +12054,7 @@
         <v>320</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E96" s="3">
         <v>0.6</v>
@@ -12063,13 +12063,13 @@
         <v>271</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="60" customHeight="1">
@@ -12083,7 +12083,7 @@
         <v>320</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E97" s="3">
         <v>0</v>
@@ -12092,13 +12092,13 @@
         <v>271</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="60" customHeight="1">
@@ -12112,7 +12112,7 @@
         <v>322</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="5" t="s">
@@ -12120,10 +12120,10 @@
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="60" customHeight="1">
@@ -12137,7 +12137,7 @@
         <v>322</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>271</v>
@@ -12145,10 +12145,10 @@
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="60" customHeight="1">
@@ -12162,7 +12162,7 @@
         <v>322</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E100" s="3">
         <v>0.6</v>
@@ -12171,13 +12171,13 @@
         <v>271</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="60" customHeight="1">
@@ -12191,7 +12191,7 @@
         <v>322</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="5" t="s">
@@ -12199,10 +12199,10 @@
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="60" customHeight="1">
@@ -12216,7 +12216,7 @@
         <v>324</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="5" t="s">
@@ -12224,10 +12224,10 @@
       </c>
       <c r="G102" s="3"/>
       <c r="H102" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="60" customHeight="1">
@@ -12241,7 +12241,7 @@
         <v>324</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>271</v>
@@ -12249,10 +12249,10 @@
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="60" customHeight="1">
@@ -12266,7 +12266,7 @@
         <v>324</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E104" s="3">
         <v>0.6</v>
@@ -12275,13 +12275,13 @@
         <v>271</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="60" customHeight="1">
@@ -12295,7 +12295,7 @@
         <v>324</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E105" s="3">
         <v>0.6</v>
@@ -12304,13 +12304,13 @@
         <v>271</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="60" customHeight="1">
@@ -12324,7 +12324,7 @@
         <v>326</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="5" t="s">
@@ -12332,10 +12332,10 @@
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="60" customHeight="1">
@@ -12349,7 +12349,7 @@
         <v>326</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E107" s="5" t="s">
         <v>271</v>
@@ -12357,10 +12357,10 @@
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="60" customHeight="1">
@@ -12374,7 +12374,7 @@
         <v>326</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="5" t="s">
@@ -12382,10 +12382,10 @@
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="60" customHeight="1">
@@ -12399,7 +12399,7 @@
         <v>326</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="5" t="s">
@@ -12407,10 +12407,10 @@
       </c>
       <c r="G109" s="3"/>
       <c r="H109" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="60" customHeight="1">
@@ -12424,7 +12424,7 @@
         <v>328</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="5" t="s">
@@ -12432,10 +12432,10 @@
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="60" customHeight="1">
@@ -12449,7 +12449,7 @@
         <v>328</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>271</v>
@@ -12457,10 +12457,10 @@
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
       <c r="H111" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="60" customHeight="1">
@@ -12474,7 +12474,7 @@
         <v>328</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="5" t="s">
@@ -12482,10 +12482,10 @@
       </c>
       <c r="G112" s="3"/>
       <c r="H112" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="60" customHeight="1">
@@ -12499,7 +12499,7 @@
         <v>328</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="5" t="s">
@@ -12507,10 +12507,10 @@
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="60" customHeight="1">
@@ -12524,7 +12524,7 @@
         <v>330</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E114" s="3">
         <v>-0.7</v>
@@ -12533,13 +12533,13 @@
         <v>271</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="60" customHeight="1">
@@ -12553,22 +12553,22 @@
         <v>330</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="60" customHeight="1">
@@ -12582,7 +12582,7 @@
         <v>330</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="5" t="s">
@@ -12590,10 +12590,10 @@
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="60" customHeight="1">
@@ -12607,7 +12607,7 @@
         <v>330</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="5" t="s">
@@ -12615,10 +12615,10 @@
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="60" customHeight="1">
@@ -12632,7 +12632,7 @@
         <v>332</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E118" s="3">
         <v>-0.7</v>
@@ -12641,13 +12641,13 @@
         <v>271</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="60" customHeight="1">
@@ -12661,22 +12661,22 @@
         <v>332</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E119" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="60" customHeight="1">
@@ -12690,7 +12690,7 @@
         <v>332</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="5" t="s">
@@ -12698,10 +12698,10 @@
       </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="60" customHeight="1">
@@ -12715,7 +12715,7 @@
         <v>332</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="5" t="s">
@@ -12723,10 +12723,10 @@
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="60" customHeight="1">
@@ -12740,7 +12740,7 @@
         <v>334</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="5" t="s">
@@ -12748,10 +12748,10 @@
       </c>
       <c r="G122" s="3"/>
       <c r="H122" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="60" customHeight="1">
@@ -12765,7 +12765,7 @@
         <v>334</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>271</v>
@@ -12773,10 +12773,10 @@
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
       <c r="H123" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="60" customHeight="1">
@@ -12790,7 +12790,7 @@
         <v>334</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E124" s="3">
         <v>0</v>
@@ -12799,13 +12799,13 @@
         <v>271</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="60" customHeight="1">
@@ -12819,7 +12819,7 @@
         <v>334</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="5" t="s">
@@ -12827,10 +12827,10 @@
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="60" customHeight="1">
@@ -12844,7 +12844,7 @@
         <v>336</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="5" t="s">
@@ -12852,10 +12852,10 @@
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="60" customHeight="1">
@@ -12869,7 +12869,7 @@
         <v>336</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>271</v>
@@ -12877,10 +12877,10 @@
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
       <c r="H127" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="60" customHeight="1">
@@ -12894,7 +12894,7 @@
         <v>336</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="5" t="s">
@@ -12902,10 +12902,10 @@
       </c>
       <c r="G128" s="3"/>
       <c r="H128" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="60" customHeight="1">
@@ -12919,7 +12919,7 @@
         <v>336</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="5" t="s">
@@ -12927,10 +12927,10 @@
       </c>
       <c r="G129" s="3"/>
       <c r="H129" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="60" customHeight="1">
@@ -12944,7 +12944,7 @@
         <v>338</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E130" s="3">
         <v>0</v>
@@ -12953,13 +12953,13 @@
         <v>271</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="60" customHeight="1">
@@ -12973,22 +12973,22 @@
         <v>338</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>271</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="60" customHeight="1">
@@ -13002,7 +13002,7 @@
         <v>338</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="5" t="s">
@@ -13010,10 +13010,10 @@
       </c>
       <c r="G132" s="3"/>
       <c r="H132" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="60" customHeight="1">
@@ -13027,7 +13027,7 @@
         <v>338</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="5" t="s">
@@ -13035,10 +13035,10 @@
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="60" customHeight="1">
@@ -13052,7 +13052,7 @@
         <v>340</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="5" t="s">
@@ -13060,10 +13060,10 @@
       </c>
       <c r="G134" s="3"/>
       <c r="H134" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="60" customHeight="1">
@@ -13077,7 +13077,7 @@
         <v>340</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>271</v>
@@ -13085,10 +13085,10 @@
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
       <c r="H135" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="60" customHeight="1">
@@ -13102,7 +13102,7 @@
         <v>340</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E136" s="3">
         <v>0.6</v>
@@ -13111,13 +13111,13 @@
         <v>271</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="60" customHeight="1">
@@ -13131,7 +13131,7 @@
         <v>340</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="5" t="s">
@@ -13139,10 +13139,10 @@
       </c>
       <c r="G137" s="3"/>
       <c r="H137" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="60" customHeight="1">
@@ -13156,7 +13156,7 @@
         <v>342</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="5" t="s">
@@ -13164,10 +13164,10 @@
       </c>
       <c r="G138" s="3"/>
       <c r="H138" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="60" customHeight="1">
@@ -13181,7 +13181,7 @@
         <v>342</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>271</v>
@@ -13189,10 +13189,10 @@
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
       <c r="H139" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="60" customHeight="1">
@@ -13206,7 +13206,7 @@
         <v>342</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E140" s="3"/>
       <c r="F140" s="5" t="s">
@@ -13214,10 +13214,10 @@
       </c>
       <c r="G140" s="3"/>
       <c r="H140" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="60" customHeight="1">
@@ -13231,7 +13231,7 @@
         <v>342</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="5" t="s">
@@ -13239,10 +13239,10 @@
       </c>
       <c r="G141" s="3"/>
       <c r="H141" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="60" customHeight="1">
@@ -13256,7 +13256,7 @@
         <v>344</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E142" s="3"/>
       <c r="F142" s="5" t="s">
@@ -13264,10 +13264,10 @@
       </c>
       <c r="G142" s="3"/>
       <c r="H142" s="3" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="60" customHeight="1">
@@ -13281,7 +13281,7 @@
         <v>344</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E143" s="5" t="s">
         <v>271</v>
@@ -13289,10 +13289,10 @@
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
       <c r="H143" s="3" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="60" customHeight="1">
@@ -13306,7 +13306,7 @@
         <v>344</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="5" t="s">
@@ -13314,10 +13314,10 @@
       </c>
       <c r="G144" s="3"/>
       <c r="H144" s="3" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="60" customHeight="1">
@@ -13331,7 +13331,7 @@
         <v>344</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E145" s="3"/>
       <c r="F145" s="5" t="s">
@@ -13339,10 +13339,10 @@
       </c>
       <c r="G145" s="3"/>
       <c r="H145" s="3" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
   </sheetData>
